--- a/artfynd/A 52205-2025 artfynd.xlsx
+++ b/artfynd/A 52205-2025 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104160498</v>
+        <v>112607019</v>
       </c>
       <c r="B2" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761552.9069179744</v>
+        <v>761223</v>
       </c>
       <c r="R2" t="n">
-        <v>7463025.5196304</v>
+        <v>7463231</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104160502</v>
+        <v>112607014</v>
       </c>
       <c r="B3" t="n">
-        <v>90645</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761223.0616051417</v>
+        <v>761724</v>
       </c>
       <c r="R3" t="n">
-        <v>7463231.273475599</v>
+        <v>7462876</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,24 +845,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,19 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104160500</v>
+        <v>112607015</v>
       </c>
       <c r="B4" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -949,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>761339.8893516522</v>
+        <v>761553</v>
       </c>
       <c r="R4" t="n">
-        <v>7463392.697157916</v>
+        <v>7463025</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,24 +947,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104160501</v>
+        <v>112607016</v>
       </c>
       <c r="B5" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>761218.1960866987</v>
+        <v>761408</v>
       </c>
       <c r="R5" t="n">
-        <v>7463237.050044856</v>
+        <v>7462981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,24 +1049,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104160497</v>
+        <v>112607017</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1183,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>761723.6072991114</v>
+        <v>761340</v>
       </c>
       <c r="R6" t="n">
-        <v>7462875.734885176</v>
+        <v>7463393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,24 +1151,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104160503</v>
+        <v>112607018</v>
       </c>
       <c r="B7" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1300,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>761361.2048776498</v>
+        <v>761218</v>
       </c>
       <c r="R7" t="n">
-        <v>7463086.123047089</v>
+        <v>7463237</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1333,24 +1253,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1377,19 +1287,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104160506</v>
+        <v>112607020</v>
       </c>
       <c r="B8" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1417,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761566.0517276976</v>
+        <v>761361</v>
       </c>
       <c r="R8" t="n">
-        <v>7462854.873000696</v>
+        <v>7463086</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1450,24 +1355,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,19 +1389,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104160505</v>
+        <v>112607021</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1534,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761456.1432864754</v>
+        <v>761456</v>
       </c>
       <c r="R9" t="n">
-        <v>7463071.164798345</v>
+        <v>7463071</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1567,24 +1457,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1611,19 +1491,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104160499</v>
+        <v>112607022</v>
       </c>
       <c r="B10" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1651,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761408.2765231156</v>
+        <v>761566</v>
       </c>
       <c r="R10" t="n">
-        <v>7462980.530661717</v>
+        <v>7462855</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1684,24 +1559,14 @@
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-09-09</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad i samband med Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 52205-2025 artfynd.xlsx
+++ b/artfynd/A 52205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607019</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607014</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607015</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607016</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607017</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607018</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1386,6 +1421,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607020</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1488,6 +1528,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607021</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,8 +1635,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112607022</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>